--- a/poc-output/m9-chromium/export-selected.xlsx
+++ b/poc-output/m9-chromium/export-selected.xlsx
@@ -293,7 +293,7 @@
         <v>46296.41673611111</v>
       </c>
       <c r="P2" s="3">
-        <v>46317.51144693287</v>
+        <v>46317.531802557874</v>
       </c>
       <c r="Q2" s="8">
         <v>1</v>
@@ -365,7 +365,7 @@
         <v>46296.41674768519</v>
       </c>
       <c r="P3" s="3">
-        <v>46317.51144693287</v>
+        <v>46317.531802557874</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -442,7 +442,7 @@
         <v>46296.41672453703</v>
       </c>
       <c r="P4" s="3">
-        <v>46317.51151986112</v>
+        <v>46317.53187128472</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>

--- a/poc-output/m9-chromium/export-selected.xlsx
+++ b/poc-output/m9-chromium/export-selected.xlsx
@@ -293,7 +293,7 @@
         <v>46296.41673611111</v>
       </c>
       <c r="P2" s="3">
-        <v>46317.531802557874</v>
+        <v>46317.537387372686</v>
       </c>
       <c r="Q2" s="8">
         <v>1</v>
@@ -365,7 +365,7 @@
         <v>46296.41674768519</v>
       </c>
       <c r="P3" s="3">
-        <v>46317.531802557874</v>
+        <v>46317.537387372686</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -442,7 +442,7 @@
         <v>46296.41672453703</v>
       </c>
       <c r="P4" s="3">
-        <v>46317.53187128472</v>
+        <v>46317.537456377315</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>

--- a/poc-output/m9-chromium/export-selected.xlsx
+++ b/poc-output/m9-chromium/export-selected.xlsx
@@ -293,7 +293,7 @@
         <v>46296.41673611111</v>
       </c>
       <c r="P2" s="3">
-        <v>46317.537387372686</v>
+        <v>46317.62256315972</v>
       </c>
       <c r="Q2" s="8">
         <v>1</v>
@@ -365,7 +365,7 @@
         <v>46296.41674768519</v>
       </c>
       <c r="P3" s="3">
-        <v>46317.537387372686</v>
+        <v>46317.62256315972</v>
       </c>
       <c r="Q3" s="8">
         <v>0</v>
@@ -442,7 +442,7 @@
         <v>46296.41672453703</v>
       </c>
       <c r="P4" s="3">
-        <v>46317.537456377315</v>
+        <v>46317.6226378125</v>
       </c>
       <c r="Q4" s="8">
         <v>0</v>
